--- a/AAII_Financials/Quarterly/SNEX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNEX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="92">
   <si>
     <t>SNEX</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>39682100</v>
+      </c>
+      <c r="E8" s="3">
         <v>45273300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>38541900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>32287100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>34437400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>36559300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>27613900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>30801200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>26748600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>21830700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>19323800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>16369100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>14817000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>15967400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>13011600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>16381000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>18930900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>16382700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>14341400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>11846800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>10192100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>11244800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>9250500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>14284900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8243400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>20366300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>11245000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>11279600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7873000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7192200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6552200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>6078800</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>39002300</v>
+      </c>
+      <c r="E9" s="3">
         <v>44490500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>37858000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>31736800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>33980500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>36100700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>27152300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>30376700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>26309000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>21437200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>18930200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>15994000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>14409100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>15593700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>12525500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>15886800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>18440900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>15862700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>13918400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>11481000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9785200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>10795000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8890800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>13967600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>7936200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>20029500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>11002000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>11033500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>7632100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>6959500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>6320500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>5860900</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>679800</v>
+      </c>
+      <c r="E10" s="3">
         <v>782800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>683900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>550300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>456900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>458600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>461600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>424500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>439600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>393500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>393600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>375100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>407900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>373700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>486100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>494200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>490000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>520000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>423000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>365800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>406900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>449800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>359700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>317300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>307200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>336800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>243000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>246100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>240900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>232700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>231700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>217900</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,82 +1338,85 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E14" s="3">
         <v>11100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-5800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>12100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-23500</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3">
         <v>-6400</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1419,8 +1439,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1428,97 +1451,100 @@
         <v>26900</v>
       </c>
       <c r="E15" s="3">
+        <v>26900</v>
+      </c>
+      <c r="F15" s="3">
         <v>25000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>21300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>14900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>15600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>15700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>17300</v>
-      </c>
-      <c r="K15" s="3">
-        <v>12300</v>
       </c>
       <c r="L15" s="3">
         <v>12300</v>
       </c>
       <c r="M15" s="3">
+        <v>12300</v>
+      </c>
+      <c r="N15" s="3">
         <v>11200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>11400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>13800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>13100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>12700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>12300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>11700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>11300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>9100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>9800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>9700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>8600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>8400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>7200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>4400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>4200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>3900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>4400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>3500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>3200</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>2900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>39516400</v>
+      </c>
+      <c r="E17" s="3">
         <v>45032400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>38354000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>32176700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>34349100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>36460200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>27497500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>30701700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>26658300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>21764200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>19226800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16294100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>14721800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>15897800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>12916000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>16314600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>18860000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>16295300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>14288900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>11841900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10146100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>11168500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>9223600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>14205000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8194400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>20310200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>11223300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>11245500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>7851400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>7161300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>6527800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>6058300</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>165700</v>
+      </c>
+      <c r="E18" s="3">
         <v>240900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>187900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>110400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>88300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>99100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>116400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>99500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>90300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>66500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>97000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>75000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>95200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>69600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>95600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>66400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>70900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>87400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>52500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>4900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>46000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>76300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>26900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>79900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>49000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>56100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>21700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>34100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>21600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>30900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>24400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>20500</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,17 +1815,18 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3">
         <v>2700</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F20" s="3" t="s">
         <v>8</v>
       </c>
@@ -1817,17 +1851,17 @@
       <c r="M20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -1880,106 +1914,112 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>192600</v>
+      </c>
+      <c r="E21" s="3">
         <v>265100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>212900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>131700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>103200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>114700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>132100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>116800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>102600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>78800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>108200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>86200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>109000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>82700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>108300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>78700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>82600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>98700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>61600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>14700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>55700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>84900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>35300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>87100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>53400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>60300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>25600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>38500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>25100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>34100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>27300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>23700</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2022,8 +2062,8 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2076,204 +2116,213 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>159800</v>
+      </c>
+      <c r="E23" s="3">
         <v>227100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>184900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>109200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>85600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>97100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>116900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>98100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>88000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>72300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>95700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>75400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>94500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>57500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>95600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>66400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>70900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>87400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>52500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>46000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>76300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>26900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>79900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>49000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>56100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>21700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>34100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>21600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>30900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>24400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>20500</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E24" s="3">
         <v>52800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>45900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>23500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>22200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>25400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>31800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>21400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>26100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>19200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>26600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>24700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>25000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>15800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>19000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>14100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>21800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>23400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>10800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-2400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>11800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>21000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>7400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>12400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>16800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>5400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>6900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>5300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>7500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>6200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>127900</v>
+      </c>
+      <c r="E26" s="3">
         <v>174300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>139000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>85700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>63400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>71700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>85100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>76700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>61900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>53100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>69100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>50700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>69500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>41700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>76600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>52300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>49100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>64000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>41700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>7300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>34200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>55300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>19500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>77400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>36600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>39300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>16300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>27200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>16300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>23400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>18200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>124200</v>
+      </c>
+      <c r="E27" s="3">
         <v>168900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>134400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>82600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>61000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>69600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>82400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>74100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>59700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>51200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>66700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>48900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>67100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>40200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>74200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>50700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>47600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>62200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>40500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>7000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>33100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>53600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>19000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>75500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>35700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>38400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>16000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>26700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>16000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>23000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>17900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>15100</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2741,8 +2802,8 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2759,11 +2820,14 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI29" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,17 +3025,20 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2700</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F32" s="3" t="s">
         <v>8</v>
       </c>
@@ -2993,17 +3063,17 @@
       <c r="M32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -3056,106 +3126,112 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>127900</v>
+      </c>
+      <c r="E33" s="3">
         <v>174300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>139000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>85700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>63400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>71700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>85100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>76700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>61900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>53100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>69100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>50700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>69500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>41700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>74200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>50700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>47600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>62200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>40500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>7000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>33100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>53600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>19000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>75500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>35700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>38400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>16000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>26700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>16000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>23000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>17900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>127900</v>
+      </c>
+      <c r="E35" s="3">
         <v>174300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>139000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>85700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>63400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>71700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>85100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>76700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>61900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>53100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>69100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>50700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>69500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>41700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>74200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>50700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>47600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>62200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>40500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>7000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>33100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>53600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>19000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>75500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>35700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>38400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>16000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>26700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>16000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>23000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>17900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,151 +3611,155 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2194300</v>
+      </c>
+      <c r="E41" s="3">
         <v>2122600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1592700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1605800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1313100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1307300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1398200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1269000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1220800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1305100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1157600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1108300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1401300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1263900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1252100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1108500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1363700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1299700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>983400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1109600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1075600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1001500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1033700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>952600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>465200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>519500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>338900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>471300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>345000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>274400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>358200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>342300</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>36233300</v>
+      </c>
+      <c r="E42" s="3">
         <v>35246900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>31792000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>26943900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>22543700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>19772700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>17674600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>16472100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>14966300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>13680100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>12633300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>11579700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>11534000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>10938300</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -3721,151 +3811,157 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>12784000</v>
+      </c>
+      <c r="E43" s="3">
         <v>13551700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>11329000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>14270300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8891400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8643900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8901100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8315600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8470500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9032800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8325800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8157200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>8026800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8615600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>603000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>583000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>636800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>626100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>550800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>487700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>634100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>494200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>268300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>428000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>411600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>482600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>333700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>427500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>283800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>305600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>352700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>288300</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1165500</v>
+      </c>
+      <c r="E44" s="3">
         <v>1038800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1373900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>917500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>705400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>796200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>861400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>681100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>587400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>616900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>518400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>537300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>444700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>572100</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
       <c r="R44" s="3">
         <v>0</v>
       </c>
@@ -3917,8 +4013,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3961,48 +4060,48 @@
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R45" s="3">
         <v>9194900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>10109800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>9803900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>9486400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>7888100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>7567300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>6943200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>6464000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>5794000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>5550100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>4541900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>4535600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3760400</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4015,53 +4114,56 @@
       <c r="AH45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>52377100</v>
+      </c>
+      <c r="E46" s="3">
         <v>51960000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>46087600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>43737500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>33453600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>30520100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>28835300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>26737800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>25245000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>24997900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>22635100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>21382500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>21406800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>21389900</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4113,8 +4215,11 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4157,258 +4262,267 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R47" s="3">
         <v>7650400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7054200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>6563400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>8776700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>8819200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>8763700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>7198300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>6952300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>6020500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>5865600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>6061300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>4853400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>5214000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>5025800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>5141400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>5131500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>4210700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>3154900</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>342600</v>
+      </c>
+      <c r="E48" s="3">
         <v>337100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>324300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>328500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>310100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>306100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>304800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>300100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>299600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>280600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>264900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>245600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>240500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>235400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>235800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>234700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>223600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>222600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>216900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>218600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>221000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>183200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>172500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>163600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>126600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>74600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>76400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>43900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>45700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>45600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>44700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>42400</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>735000</v>
+      </c>
+      <c r="E49" s="3">
         <v>743800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>755000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>736200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>88900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>90000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>87000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>80600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>77100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>79500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>80500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>82400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>85200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>88900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>91500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>86200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>90000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>93500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>97200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>100800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>98700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>102500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>106400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>109500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>76300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>73100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>71500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>67900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>65900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>59400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>59300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>59800</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>563700</v>
+      </c>
+      <c r="E52" s="3">
         <v>555700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>590200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>433800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>373700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>316400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>304600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>301500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>266800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>250700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>226900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>182800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>167700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>169200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>40000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>52000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>43000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>41800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>35500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>35100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>37000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>35200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>39300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>36900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>363400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>14000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>18600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3608400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>3763200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>3248600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>3404100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>3663000</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>54046000</v>
+      </c>
+      <c r="E54" s="3">
         <v>53626900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>47784400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>45268000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>34265600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>31282900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>29585300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>27466300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>25930800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>25651000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>23244800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>21938700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>21933100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>21918900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>19832400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>19859600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>19408800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>21195700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>19229000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>18839600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>16799800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>15799700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>13974800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>13474900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>12389500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>10870900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>10129300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>9936100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>10054900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>9407700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>8710500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>7824700</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,347 +5099,357 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>24202200</v>
+      </c>
+      <c r="E57" s="3">
         <v>25339000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>20830800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>21562300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>12038900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11822600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>12225500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11597700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11560300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12047200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11034600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10948000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10832000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>11239500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>9950400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>10951400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>10914800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10352900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>8678800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>8754500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>7855900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>7347000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>6450500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>6499100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5050100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>5145500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>4113200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4013200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3963800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3698100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3629500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3874500</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>20257100</v>
+        <v>21483800</v>
       </c>
       <c r="E58" s="3">
+        <v>20266100</v>
+      </c>
+      <c r="F58" s="3">
         <v>18632500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>16697900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>15615200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>12852700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10989200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10462000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>8523500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7912700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7242400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5932200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6529400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>974200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5403500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4385100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3903200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5911600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>6838800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>6494500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>5327900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5514400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4873100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>4597400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>4990100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3869100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>4362400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>4233600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>4141600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3761200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3270300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2214600</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3479800</v>
+      </c>
+      <c r="E59" s="3">
         <v>3460300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3994700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2677600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3515400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3614000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3285500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2608900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3266700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2817200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2543700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2837000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2325400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2387400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>171300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>159200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>158900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>169000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>163100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>159800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>168000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>133000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>136900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>141300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>99500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>44800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>47000</v>
-      </c>
-      <c r="AD59" s="3">
-        <v>10400</v>
       </c>
       <c r="AE59" s="3">
         <v>10400</v>
       </c>
       <c r="AF59" s="3">
+        <v>10400</v>
+      </c>
+      <c r="AG59" s="3">
         <v>11300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>9600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>49056400</v>
+        <v>49165800</v>
       </c>
       <c r="E60" s="3">
+        <v>49065400</v>
+      </c>
+      <c r="F60" s="3">
         <v>43458000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>40939800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>31169500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>28289300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>26500200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>24670800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>23350500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>22778800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>20822500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>19719100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>19688400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>14602500</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -5361,106 +5501,112 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1764400</v>
+        <v>1935700</v>
       </c>
       <c r="E61" s="3">
+        <v>1755400</v>
+      </c>
+      <c r="F61" s="3">
         <v>1702300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1853900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1104300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1086400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1291900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1077800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>964300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1321400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>930700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>832400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>914800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6069100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>922100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>824200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>847100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>974800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>994700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>755600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>782400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>826900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>887400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>783600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>832700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>459300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>325400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>369900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>507400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>428600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>435400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>355200</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5512,8 +5658,8 @@
       <c r="S62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
+      <c r="T62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U62" s="3">
         <v>0</v>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>51202000</v>
+      </c>
+      <c r="E66" s="3">
         <v>50927600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>45262200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>42890600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>32286800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>29400900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>27807900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>25757200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>24323000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>24108400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>21762000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>20559600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>20603200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>20671600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>18655800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>18789500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>18361500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>20190100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>18276000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>17935600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>15898400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>14939500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>13175300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>12707400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>11700700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>10222300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>9514400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>9341900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>9484400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>8855900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>8184500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>7319400</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2136000</v>
+      </c>
+      <c r="E72" s="3">
         <v>2008100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1833800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1694800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1609100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1545700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1474000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1388900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1312200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1250300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1197200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1128100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1077400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1007900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>966200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>889600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>837300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>788200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>724200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>682500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>675200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>641000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>585700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>572400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>495000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>458400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>419100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>402100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>374900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>358600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>335200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>317000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2844000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2699300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2522200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2377400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1978800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1882000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1777400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1709100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1607800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1542600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1482800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1379100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1329900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1247300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1176600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1070100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1047300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1005600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>953000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>904000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>901400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>860200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>799500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>767500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>688800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>648600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>614900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>594200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>570500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>551800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>526000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>505300</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>127900</v>
+      </c>
+      <c r="E81" s="3">
         <v>174300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>139000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>85700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>63400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>71700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>85100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>76700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>61900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>53100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>69100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>50700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>69500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>41700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>74200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>50700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>47600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>62200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>40500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>7000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>33100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>53600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>19000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>75500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>35700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>38400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>16000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>26700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>16000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>23000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>17900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,106 +7400,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E83" s="3">
         <v>21300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>22300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>20900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>17700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>16100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>12400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>14700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>12100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>11300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>12200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>12700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>12400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>11600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>12700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>12300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>11700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>11300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>9100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>9800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>9700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>8600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>8400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>7200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>4400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>4200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>3900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>4400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>3500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>3200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>2900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1208400</v>
+      </c>
+      <c r="E89" s="3">
         <v>2798600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1261700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3529400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1491200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-154500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-477800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>192600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-622100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>784000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>152400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>371100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>207900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1649400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1046700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>266500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2598000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2702200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-600200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>744100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>713600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>783800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-118800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>743400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>37200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>502400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>667600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-130000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>462500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>76100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-213000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-21300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-15200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-20500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-16000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-15300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-13600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-16700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-18400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-17400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-12700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-14100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-10300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-11300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-11900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-13300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-17000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-7300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-8600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-13500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-17600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-22400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-11100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-4500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-19200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-28100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-406600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-16200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-21100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-21600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-18700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-18900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-13400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-12700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-14100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-10300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-10800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-17800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-11900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-13500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-16800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-7300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-9000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-10400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-17600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-22800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-226300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-5400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-6900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-9900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-5200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-6100</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8396,8 +8630,8 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>101300</v>
+      </c>
+      <c r="E100" s="3">
         <v>79800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-299800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>918700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>14400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-206500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>188200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>113800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-382800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>380100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>76900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-81700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-140000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-36200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>88600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-25400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-131000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-19300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>241500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-35000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-47000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-58100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>104500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-146000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>374200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>127800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-43700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-141000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>78600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-7600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>79600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E101" s="3">
         <v>11700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-18400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>6600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-9100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>6800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-12200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>3700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>3000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>8100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-5700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-5400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>8100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-5700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-5400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-2900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>4000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>14100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>300</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
       <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
         <v>300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-7100</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1122300</v>
+      </c>
+      <c r="E102" s="3">
         <v>2859700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1590500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4047100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1500500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-370400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-329600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>294300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1032900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1146100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>223400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>263100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>61300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1693400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1125600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>223500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2747900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2667500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-367500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>697200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>660200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>706700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-23000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>369600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>408400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>621400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>617700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-274800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>518200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>58600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-138300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-5500</v>
       </c>
     </row>
